--- a/histograms/histogram_Bandgap__eV.xlsx
+++ b/histograms/histogram_Bandgap__eV.xlsx
@@ -445,7 +445,7 @@
         <v>1.44375</v>
       </c>
       <c r="B2" t="n">
-        <v>524</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
@@ -469,7 +469,7 @@
         <v>2.00625</v>
       </c>
       <c r="B5" t="n">
-        <v>102</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -477,7 +477,7 @@
         <v>2.19375</v>
       </c>
       <c r="B6" t="n">
-        <v>813</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7">
@@ -485,7 +485,7 @@
         <v>2.38125</v>
       </c>
       <c r="B7" t="n">
-        <v>1095</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8">
@@ -493,7 +493,7 @@
         <v>2.56875</v>
       </c>
       <c r="B8" t="n">
-        <v>1032</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9">
@@ -501,7 +501,7 @@
         <v>2.75625</v>
       </c>
       <c r="B9" t="n">
-        <v>292</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10">
@@ -509,7 +509,7 @@
         <v>2.94375</v>
       </c>
       <c r="B10" t="n">
-        <v>1437</v>
+        <v>35</v>
       </c>
     </row>
     <row r="11">
@@ -517,7 +517,7 @@
         <v>3.13125</v>
       </c>
       <c r="B11" t="n">
-        <v>3721</v>
+        <v>85</v>
       </c>
     </row>
     <row r="12">
@@ -525,7 +525,7 @@
         <v>3.31875</v>
       </c>
       <c r="B12" t="n">
-        <v>7651</v>
+        <v>171</v>
       </c>
     </row>
     <row r="13">
@@ -533,7 +533,7 @@
         <v>3.50625</v>
       </c>
       <c r="B13" t="n">
-        <v>5954</v>
+        <v>192</v>
       </c>
     </row>
     <row r="14">
@@ -541,7 +541,7 @@
         <v>3.69375</v>
       </c>
       <c r="B14" t="n">
-        <v>1414</v>
+        <v>44</v>
       </c>
     </row>
     <row r="15">
@@ -549,7 +549,7 @@
         <v>3.88125</v>
       </c>
       <c r="B15" t="n">
-        <v>1039</v>
+        <v>59</v>
       </c>
     </row>
     <row r="16">
@@ -557,7 +557,7 @@
         <v>4.06875</v>
       </c>
       <c r="B16" t="n">
-        <v>457</v>
+        <v>25</v>
       </c>
     </row>
     <row r="17">
@@ -565,7 +565,7 @@
         <v>4.25625</v>
       </c>
       <c r="B17" t="n">
-        <v>194</v>
+        <v>26</v>
       </c>
     </row>
     <row r="18">
@@ -573,7 +573,7 @@
         <v>4.44375</v>
       </c>
       <c r="B18" t="n">
-        <v>135</v>
+        <v>13</v>
       </c>
     </row>
     <row r="19">
@@ -581,7 +581,7 @@
         <v>4.63125</v>
       </c>
       <c r="B19" t="n">
-        <v>226</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20">
@@ -589,7 +589,7 @@
         <v>4.81875</v>
       </c>
       <c r="B20" t="n">
-        <v>76</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -597,7 +597,7 @@
         <v>5.00625</v>
       </c>
       <c r="B21" t="n">
-        <v>235</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
